--- a/bobcat-dash-BOM.xlsx
+++ b/bobcat-dash-BOM.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Titles" vbProcedure="false">BOM!$5:$5</definedName>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">BOM!$A$5:$K$86</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">BOM!$A$5:$K$92</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="252">
   <si>
     <t xml:space="preserve">Bobcat Digital Dash — Bill of Materials</t>
   </si>
@@ -558,6 +558,63 @@
   </si>
   <si>
     <t xml:space="preserve">Subtotal — Lights</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MACHINE ANGLE (roll / pitch): README, Machine angle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Accelerometer + gyro board</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LSM6DSOX 6-DoF, I2C, 3.3 V (or LSM6DS3TR-C, Adafruit 4503)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adafruit 4438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">README: Machine angle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mount rigidly to the frame, flat, X arrow forward. I2C address 0x6A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Micro-Fit 3.0 receptacle housing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4-position, single row, latching</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Molex 43645-0400</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Board README: TILT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plugs into the board's TILT header J13 (43650-0415)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Micro-Fit 3.0 crimp pins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Female, 20-24 AWG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Molex 43030-0007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crimp tool for Micro-Fit, or buy pre-crimped Micro-Fit leads</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sensor cable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22-24 AWG, 4-core, shielded if possible, under ~30-50 cm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Your 14/16 AWG harness wire won't fit the Micro-Fit pins or the sensor board. Solder this end into the sensor board; shield to GND at the board end only</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Subtotal — Machine Angle</t>
   </si>
   <si>
     <t xml:space="preserve">CHARGING: Delco 10SI 3-wire alternator (wiring-schematic.jpg, section 7)</t>
@@ -1377,7 +1434,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:K91"/>
+  <dimension ref="A1:K97"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="6"/>
@@ -3014,7 +3071,7 @@
       <c r="J66" s="5"/>
       <c r="K66" s="5"/>
     </row>
-    <row r="67" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="6" t="n">
         <v>47</v>
       </c>
@@ -3044,7 +3101,7 @@
       <c r="J67" s="11"/>
       <c r="K67" s="12"/>
     </row>
-    <row r="68" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="6" t="n">
         <v>48</v>
       </c>
@@ -3058,13 +3115,13 @@
         <v>185</v>
       </c>
       <c r="E68" s="8" t="s">
-        <v>23</v>
+        <v>186</v>
       </c>
       <c r="F68" s="6" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="G68" s="8" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="H68" s="9"/>
       <c r="I68" s="10" t="n">
@@ -3074,27 +3131,27 @@
       <c r="J68" s="11"/>
       <c r="K68" s="12"/>
     </row>
-    <row r="69" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="6" t="n">
         <v>49</v>
       </c>
       <c r="B69" s="7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C69" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="D69" s="8" t="s">
+        <v>190</v>
+      </c>
+      <c r="E69" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="F69" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="D69" s="8" t="s">
-        <v>188</v>
-      </c>
-      <c r="E69" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="F69" s="6" t="s">
-        <v>182</v>
-      </c>
       <c r="G69" s="8" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="H69" s="9"/>
       <c r="I69" s="10" t="n">
@@ -3104,61 +3161,61 @@
       <c r="J69" s="11"/>
       <c r="K69" s="12"/>
     </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G70" s="13" t="s">
-        <v>190</v>
-      </c>
-      <c r="I70" s="14" t="n">
-        <f aca="false">SUM(I67:I69)</f>
-        <v>0</v>
-      </c>
+    <row r="70" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="B70" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C70" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="D70" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="E70" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F70" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="G70" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="H70" s="9"/>
+      <c r="I70" s="10" t="n">
+        <f aca="false">B70*H70</f>
+        <v>0</v>
+      </c>
+      <c r="J70" s="11"/>
+      <c r="K70" s="12"/>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="5" t="s">
-        <v>191</v>
-      </c>
-      <c r="B71" s="5"/>
-      <c r="C71" s="5"/>
-      <c r="D71" s="5"/>
-      <c r="E71" s="5"/>
-      <c r="F71" s="5"/>
-      <c r="G71" s="5"/>
-      <c r="H71" s="5"/>
-      <c r="I71" s="5"/>
-      <c r="J71" s="5"/>
-      <c r="K71" s="5"/>
+      <c r="G71" s="13" t="s">
+        <v>196</v>
+      </c>
+      <c r="I71" s="14" t="n">
+        <f aca="false">SUM(I67:I70)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="B72" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C72" s="8" t="s">
-        <v>192</v>
-      </c>
-      <c r="D72" s="8" t="s">
-        <v>193</v>
-      </c>
-      <c r="E72" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="F72" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="G72" s="8" t="s">
-        <v>194</v>
-      </c>
-      <c r="H72" s="9"/>
-      <c r="I72" s="10" t="n">
-        <f aca="false">B72*H72</f>
-        <v>0</v>
-      </c>
-      <c r="J72" s="11"/>
-      <c r="K72" s="12"/>
-    </row>
-    <row r="73" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="B72" s="5"/>
+      <c r="C72" s="5"/>
+      <c r="D72" s="5"/>
+      <c r="E72" s="5"/>
+      <c r="F72" s="5"/>
+      <c r="G72" s="5"/>
+      <c r="H72" s="5"/>
+      <c r="I72" s="5"/>
+      <c r="J72" s="5"/>
+      <c r="K72" s="5"/>
+    </row>
+    <row r="73" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="6" t="n">
         <v>51</v>
       </c>
@@ -3166,19 +3223,19 @@
         <v>1</v>
       </c>
       <c r="C73" s="8" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="D73" s="8" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="E73" s="8" t="s">
-        <v>23</v>
+        <v>200</v>
       </c>
       <c r="F73" s="6" t="s">
-        <v>23</v>
+        <v>201</v>
       </c>
       <c r="G73" s="8" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="H73" s="9"/>
       <c r="I73" s="10" t="n">
@@ -3188,7 +3245,7 @@
       <c r="J73" s="11"/>
       <c r="K73" s="12"/>
     </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="6" t="n">
         <v>52</v>
       </c>
@@ -3196,19 +3253,19 @@
         <v>1</v>
       </c>
       <c r="C74" s="8" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="D74" s="8" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="E74" s="8" t="s">
         <v>23</v>
       </c>
       <c r="F74" s="6" t="s">
-        <v>23</v>
+        <v>201</v>
       </c>
       <c r="G74" s="8" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="H74" s="9"/>
       <c r="I74" s="10" t="n">
@@ -3218,7 +3275,7 @@
       <c r="J74" s="11"/>
       <c r="K74" s="12"/>
     </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="6" t="n">
         <v>53</v>
       </c>
@@ -3226,19 +3283,19 @@
         <v>1</v>
       </c>
       <c r="C75" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="D75" s="8" t="s">
+        <v>207</v>
+      </c>
+      <c r="E75" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F75" s="6" t="s">
         <v>201</v>
       </c>
-      <c r="D75" s="8" t="s">
-        <v>202</v>
-      </c>
-      <c r="E75" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="F75" s="6" t="s">
-        <v>23</v>
-      </c>
       <c r="G75" s="8" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="H75" s="9"/>
       <c r="I75" s="10" t="n">
@@ -3249,77 +3306,41 @@
       <c r="K75" s="12"/>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="6" t="n">
-        <v>54</v>
-      </c>
-      <c r="B76" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C76" s="8" t="s">
-        <v>204</v>
-      </c>
-      <c r="D76" s="8" t="s">
-        <v>205</v>
-      </c>
-      <c r="E76" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="F76" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="G76" s="8" t="s">
-        <v>206</v>
-      </c>
-      <c r="H76" s="9"/>
-      <c r="I76" s="10" t="n">
-        <f aca="false">B76*H76</f>
-        <v>0</v>
-      </c>
-      <c r="J76" s="11"/>
-      <c r="K76" s="12"/>
+      <c r="G76" s="13" t="s">
+        <v>209</v>
+      </c>
+      <c r="I76" s="14" t="n">
+        <f aca="false">SUM(I73:I75)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="6" t="n">
-        <v>55</v>
-      </c>
-      <c r="B77" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C77" s="8" t="s">
-        <v>207</v>
-      </c>
-      <c r="D77" s="8" t="s">
-        <v>208</v>
-      </c>
-      <c r="E77" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="F77" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="G77" s="8" t="s">
-        <v>200</v>
-      </c>
-      <c r="H77" s="9"/>
-      <c r="I77" s="10" t="n">
-        <f aca="false">B77*H77</f>
-        <v>0</v>
-      </c>
-      <c r="J77" s="11"/>
-      <c r="K77" s="12"/>
+      <c r="A77" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="B77" s="5"/>
+      <c r="C77" s="5"/>
+      <c r="D77" s="5"/>
+      <c r="E77" s="5"/>
+      <c r="F77" s="5"/>
+      <c r="G77" s="5"/>
+      <c r="H77" s="5"/>
+      <c r="I77" s="5"/>
+      <c r="J77" s="5"/>
+      <c r="K77" s="5"/>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="6" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B78" s="7" t="n">
         <v>1</v>
       </c>
       <c r="C78" s="8" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="D78" s="8" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="E78" s="8" t="s">
         <v>23</v>
@@ -3328,7 +3349,7 @@
         <v>23</v>
       </c>
       <c r="G78" s="8" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H78" s="9"/>
       <c r="I78" s="10" t="n">
@@ -3338,18 +3359,18 @@
       <c r="J78" s="11"/>
       <c r="K78" s="12"/>
     </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="6" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B79" s="7" t="n">
         <v>1</v>
       </c>
       <c r="C79" s="8" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="D79" s="8" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="E79" s="8" t="s">
         <v>23</v>
@@ -3358,7 +3379,7 @@
         <v>23</v>
       </c>
       <c r="G79" s="8" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="H79" s="9"/>
       <c r="I79" s="10" t="n">
@@ -3369,28 +3390,64 @@
       <c r="K79" s="12"/>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G80" s="13" t="s">
-        <v>215</v>
-      </c>
-      <c r="I80" s="14" t="n">
-        <f aca="false">SUM(I72:I79)</f>
-        <v>0</v>
-      </c>
+      <c r="A80" s="6" t="n">
+        <v>56</v>
+      </c>
+      <c r="B80" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C80" s="8" t="s">
+        <v>217</v>
+      </c>
+      <c r="D80" s="8" t="s">
+        <v>218</v>
+      </c>
+      <c r="E80" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F80" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="G80" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="H80" s="9"/>
+      <c r="I80" s="10" t="n">
+        <f aca="false">B80*H80</f>
+        <v>0</v>
+      </c>
+      <c r="J80" s="11"/>
+      <c r="K80" s="12"/>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="5" t="s">
-        <v>216</v>
-      </c>
-      <c r="B81" s="5"/>
-      <c r="C81" s="5"/>
-      <c r="D81" s="5"/>
-      <c r="E81" s="5"/>
-      <c r="F81" s="5"/>
-      <c r="G81" s="5"/>
-      <c r="H81" s="5"/>
-      <c r="I81" s="5"/>
-      <c r="J81" s="5"/>
-      <c r="K81" s="5"/>
+      <c r="A81" s="6" t="n">
+        <v>57</v>
+      </c>
+      <c r="B81" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C81" s="8" t="s">
+        <v>220</v>
+      </c>
+      <c r="D81" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="E81" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F81" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="G81" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="H81" s="9"/>
+      <c r="I81" s="10" t="n">
+        <f aca="false">B81*H81</f>
+        <v>0</v>
+      </c>
+      <c r="J81" s="11"/>
+      <c r="K81" s="12"/>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="6" t="n">
@@ -3400,19 +3457,19 @@
         <v>1</v>
       </c>
       <c r="C82" s="8" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="D82" s="8" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="E82" s="8" t="s">
         <v>23</v>
       </c>
       <c r="F82" s="6" t="s">
-        <v>61</v>
+        <v>23</v>
       </c>
       <c r="G82" s="8" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="H82" s="9"/>
       <c r="I82" s="10" t="n">
@@ -3422,7 +3479,7 @@
       <c r="J82" s="11"/>
       <c r="K82" s="12"/>
     </row>
-    <row r="83" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="6" t="n">
         <v>59</v>
       </c>
@@ -3430,19 +3487,19 @@
         <v>1</v>
       </c>
       <c r="C83" s="8" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="D83" s="8" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="E83" s="8" t="s">
         <v>23</v>
       </c>
       <c r="F83" s="6" t="s">
-        <v>61</v>
+        <v>23</v>
       </c>
       <c r="G83" s="8" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="H83" s="9"/>
       <c r="I83" s="10" t="n">
@@ -3452,7 +3509,7 @@
       <c r="J83" s="11"/>
       <c r="K83" s="12"/>
     </row>
-    <row r="84" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="6" t="n">
         <v>60</v>
       </c>
@@ -3460,19 +3517,19 @@
         <v>1</v>
       </c>
       <c r="C84" s="8" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="D84" s="8" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="E84" s="8" t="s">
         <v>23</v>
       </c>
       <c r="F84" s="6" t="s">
-        <v>61</v>
+        <v>23</v>
       </c>
       <c r="G84" s="8" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="H84" s="9"/>
       <c r="I84" s="10" t="n">
@@ -3490,19 +3547,19 @@
         <v>1</v>
       </c>
       <c r="C85" s="8" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="D85" s="8" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="E85" s="8" t="s">
         <v>23</v>
       </c>
       <c r="F85" s="6" t="s">
-        <v>72</v>
+        <v>23</v>
       </c>
       <c r="G85" s="8" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="H85" s="9"/>
       <c r="I85" s="10" t="n">
@@ -3514,43 +3571,187 @@
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G86" s="13" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="I86" s="14" t="n">
-        <f aca="false">SUM(I82:I85)</f>
-        <v>0</v>
-      </c>
+        <f aca="false">SUM(I78:I85)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="B87" s="5"/>
+      <c r="C87" s="5"/>
+      <c r="D87" s="5"/>
+      <c r="E87" s="5"/>
+      <c r="F87" s="5"/>
+      <c r="G87" s="5"/>
+      <c r="H87" s="5"/>
+      <c r="I87" s="5"/>
+      <c r="J87" s="5"/>
+      <c r="K87" s="5"/>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G88" s="15" t="s">
-        <v>230</v>
-      </c>
-      <c r="I88" s="16" t="n">
-        <f aca="false">I13+I19+I32+I38+I48+I56+I65+I70+I80+I86</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G89" s="17" t="s">
-        <v>231</v>
-      </c>
-      <c r="I89" s="18" t="n">
-        <f aca="false">COUNTIF(B6:B80,"&gt;0")-COUNTIF(K6:K80,"Y")</f>
-        <v>54</v>
-      </c>
+      <c r="A88" s="6" t="n">
+        <v>62</v>
+      </c>
+      <c r="B88" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C88" s="8" t="s">
+        <v>236</v>
+      </c>
+      <c r="D88" s="8" t="s">
+        <v>237</v>
+      </c>
+      <c r="E88" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F88" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="G88" s="8" t="s">
+        <v>238</v>
+      </c>
+      <c r="H88" s="9"/>
+      <c r="I88" s="10" t="n">
+        <f aca="false">B88*H88</f>
+        <v>0</v>
+      </c>
+      <c r="J88" s="11"/>
+      <c r="K88" s="12"/>
+    </row>
+    <row r="89" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="6" t="n">
+        <v>63</v>
+      </c>
+      <c r="B89" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C89" s="8" t="s">
+        <v>239</v>
+      </c>
+      <c r="D89" s="8" t="s">
+        <v>240</v>
+      </c>
+      <c r="E89" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F89" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="G89" s="8" t="s">
+        <v>241</v>
+      </c>
+      <c r="H89" s="9"/>
+      <c r="I89" s="10" t="n">
+        <f aca="false">B89*H89</f>
+        <v>0</v>
+      </c>
+      <c r="J89" s="11"/>
+      <c r="K89" s="12"/>
+    </row>
+    <row r="90" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="6" t="n">
+        <v>64</v>
+      </c>
+      <c r="B90" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C90" s="8" t="s">
+        <v>242</v>
+      </c>
+      <c r="D90" s="8" t="s">
+        <v>243</v>
+      </c>
+      <c r="E90" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F90" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="G90" s="8" t="s">
+        <v>244</v>
+      </c>
+      <c r="H90" s="9"/>
+      <c r="I90" s="10" t="n">
+        <f aca="false">B90*H90</f>
+        <v>0</v>
+      </c>
+      <c r="J90" s="11"/>
+      <c r="K90" s="12"/>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="19" t="s">
-        <v>232</v>
+      <c r="A91" s="6" t="n">
+        <v>65</v>
+      </c>
+      <c r="B91" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C91" s="8" t="s">
+        <v>245</v>
+      </c>
+      <c r="D91" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="E91" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F91" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="G91" s="8" t="s">
+        <v>247</v>
+      </c>
+      <c r="H91" s="9"/>
+      <c r="I91" s="10" t="n">
+        <f aca="false">B91*H91</f>
+        <v>0</v>
+      </c>
+      <c r="J91" s="11"/>
+      <c r="K91" s="12"/>
+    </row>
+    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G92" s="13" t="s">
+        <v>248</v>
+      </c>
+      <c r="I92" s="14" t="n">
+        <f aca="false">SUM(I88:I91)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G94" s="15" t="s">
+        <v>249</v>
+      </c>
+      <c r="I94" s="16" t="n">
+        <f aca="false">I13+I19+I32+I38+I48+I56+I65+I71+I76+I86+I92</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G95" s="17" t="s">
+        <v>250</v>
+      </c>
+      <c r="I95" s="18" t="n">
+        <f aca="false">COUNTIF(B6:B86,"&gt;0")-COUNTIF(K6:K86,"Y")</f>
+        <v>58</v>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="19" t="s">
+        <v>251</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A5:K86"/>
+  <autoFilter ref="A5:K92"/>
   <mergeCells count="1">
     <mergeCell ref="A3:K3"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="K7:K12 K15:K18 K21:K31 K34:K37 K40:K47 K50:K55 K58:K64 K67:K69 K72:K79 K82:K85" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="K7:K12 K15:K18 K21:K31 K34:K37 K40:K47 K50:K55 K58:K64 K67:K70 K73:K75 K78:K85 K88:K91" type="list">
       <formula1>"Y,N"</formula1>
       <formula2>0</formula2>
     </dataValidation>

--- a/bobcat-dash-BOM.xlsx
+++ b/bobcat-dash-BOM.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Titles" vbProcedure="false">BOM!$5:$5</definedName>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">BOM!$A$5:$K$92</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">BOM!$A$5:$K$97</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="252">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="263">
   <si>
     <t xml:space="preserve">Bobcat Digital Dash — Bill of Materials</t>
   </si>
@@ -440,7 +440,7 @@
     <t xml:space="preserve">Bare PCB</t>
   </si>
   <si>
-    <t xml:space="preserve">150 × 134 mm, 2 layers, 1.6 mm, 1 oz</t>
+    <t xml:space="preserve">162 × 134 mm (rev 2.7), 2 layers, 1.6 mm, 1 oz</t>
   </si>
   <si>
     <t xml:space="preserve">breakout-board/fab gerbers zip</t>
@@ -615,6 +615,39 @@
   </si>
   <si>
     <t xml:space="preserve">Subtotal — Machine Angle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TEMPERATURE: README, Temperatures</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Waterproof temperature probe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DS18B20 in a stainless tip, 3-wire cable (red 3V3, black GND, yellow/white data)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">README: Temperatures</t>
+  </si>
+  <si>
+    <t xml:space="preserve">One for the cab, one for outside air (shade it from sun and engine heat). Optional: the board measures the box itself</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3-position, single row, latching</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Molex 43645-0300</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Board README: TEMP PROBE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plugs into the board's TEMP PROBE header J14 (43650-0315)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Two probes: join their 3 wires in the cable (each wire to the same pin)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Subtotal — Temperature: Readme, Temperatures</t>
   </si>
   <si>
     <t xml:space="preserve">CHARGING: Delco 10SI 3-wire alternator (wiring-schematic.jpg, section 7)</t>
@@ -1434,7 +1467,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:K97"/>
+  <dimension ref="A1:K102"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="6"/>
@@ -3215,12 +3248,12 @@
       <c r="J72" s="5"/>
       <c r="K72" s="5"/>
     </row>
-    <row r="73" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="6" t="n">
         <v>51</v>
       </c>
       <c r="B73" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C73" s="8" t="s">
         <v>198</v>
@@ -3229,13 +3262,13 @@
         <v>199</v>
       </c>
       <c r="E73" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F73" s="6" t="s">
         <v>200</v>
       </c>
-      <c r="F73" s="6" t="s">
+      <c r="G73" s="8" t="s">
         <v>201</v>
-      </c>
-      <c r="G73" s="8" t="s">
-        <v>202</v>
       </c>
       <c r="H73" s="9"/>
       <c r="I73" s="10" t="n">
@@ -3253,16 +3286,16 @@
         <v>1</v>
       </c>
       <c r="C74" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="D74" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="E74" s="8" t="s">
         <v>203</v>
       </c>
-      <c r="D74" s="8" t="s">
+      <c r="F74" s="6" t="s">
         <v>204</v>
-      </c>
-      <c r="E74" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="F74" s="6" t="s">
-        <v>201</v>
       </c>
       <c r="G74" s="8" t="s">
         <v>205</v>
@@ -3275,27 +3308,27 @@
       <c r="J74" s="11"/>
       <c r="K74" s="12"/>
     </row>
-    <row r="75" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="6" t="n">
         <v>53</v>
       </c>
       <c r="B75" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C75" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="D75" s="8" t="s">
+        <v>190</v>
+      </c>
+      <c r="E75" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="F75" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="G75" s="8" t="s">
         <v>206</v>
-      </c>
-      <c r="D75" s="8" t="s">
-        <v>207</v>
-      </c>
-      <c r="E75" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="F75" s="6" t="s">
-        <v>201</v>
-      </c>
-      <c r="G75" s="8" t="s">
-        <v>208</v>
       </c>
       <c r="H75" s="9"/>
       <c r="I75" s="10" t="n">
@@ -3307,7 +3340,7 @@
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G76" s="13" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="I76" s="14" t="n">
         <f aca="false">SUM(I73:I75)</f>
@@ -3316,7 +3349,7 @@
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="5" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B77" s="5"/>
       <c r="C77" s="5"/>
@@ -3329,7 +3362,7 @@
       <c r="J77" s="5"/>
       <c r="K77" s="5"/>
     </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="6" t="n">
         <v>54</v>
       </c>
@@ -3337,16 +3370,16 @@
         <v>1</v>
       </c>
       <c r="C78" s="8" t="s">
+        <v>209</v>
+      </c>
+      <c r="D78" s="8" t="s">
+        <v>210</v>
+      </c>
+      <c r="E78" s="8" t="s">
         <v>211</v>
       </c>
-      <c r="D78" s="8" t="s">
+      <c r="F78" s="6" t="s">
         <v>212</v>
-      </c>
-      <c r="E78" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="F78" s="6" t="s">
-        <v>23</v>
       </c>
       <c r="G78" s="8" t="s">
         <v>213</v>
@@ -3359,7 +3392,7 @@
       <c r="J78" s="11"/>
       <c r="K78" s="12"/>
     </row>
-    <row r="79" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="6" t="n">
         <v>55</v>
       </c>
@@ -3376,7 +3409,7 @@
         <v>23</v>
       </c>
       <c r="F79" s="6" t="s">
-        <v>23</v>
+        <v>212</v>
       </c>
       <c r="G79" s="8" t="s">
         <v>216</v>
@@ -3389,7 +3422,7 @@
       <c r="J79" s="11"/>
       <c r="K79" s="12"/>
     </row>
-    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="6" t="n">
         <v>56</v>
       </c>
@@ -3406,7 +3439,7 @@
         <v>23</v>
       </c>
       <c r="F80" s="6" t="s">
-        <v>23</v>
+        <v>212</v>
       </c>
       <c r="G80" s="8" t="s">
         <v>219</v>
@@ -3420,77 +3453,41 @@
       <c r="K80" s="12"/>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="6" t="n">
-        <v>57</v>
-      </c>
-      <c r="B81" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C81" s="8" t="s">
+      <c r="G81" s="13" t="s">
         <v>220</v>
       </c>
-      <c r="D81" s="8" t="s">
+      <c r="I81" s="14" t="n">
+        <f aca="false">SUM(I78:I80)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="5" t="s">
         <v>221</v>
       </c>
-      <c r="E81" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="F81" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="G81" s="8" t="s">
-        <v>222</v>
-      </c>
-      <c r="H81" s="9"/>
-      <c r="I81" s="10" t="n">
-        <f aca="false">B81*H81</f>
-        <v>0</v>
-      </c>
-      <c r="J81" s="11"/>
-      <c r="K81" s="12"/>
-    </row>
-    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="6" t="n">
-        <v>58</v>
-      </c>
-      <c r="B82" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C82" s="8" t="s">
-        <v>223</v>
-      </c>
-      <c r="D82" s="8" t="s">
-        <v>224</v>
-      </c>
-      <c r="E82" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="F82" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="G82" s="8" t="s">
-        <v>225</v>
-      </c>
-      <c r="H82" s="9"/>
-      <c r="I82" s="10" t="n">
-        <f aca="false">B82*H82</f>
-        <v>0</v>
-      </c>
-      <c r="J82" s="11"/>
-      <c r="K82" s="12"/>
+      <c r="B82" s="5"/>
+      <c r="C82" s="5"/>
+      <c r="D82" s="5"/>
+      <c r="E82" s="5"/>
+      <c r="F82" s="5"/>
+      <c r="G82" s="5"/>
+      <c r="H82" s="5"/>
+      <c r="I82" s="5"/>
+      <c r="J82" s="5"/>
+      <c r="K82" s="5"/>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="6" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B83" s="7" t="n">
         <v>1</v>
       </c>
       <c r="C83" s="8" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="D83" s="8" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="E83" s="8" t="s">
         <v>23</v>
@@ -3499,7 +3496,7 @@
         <v>23</v>
       </c>
       <c r="G83" s="8" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="H83" s="9"/>
       <c r="I83" s="10" t="n">
@@ -3509,18 +3506,18 @@
       <c r="J83" s="11"/>
       <c r="K83" s="12"/>
     </row>
-    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="84" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="6" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B84" s="7" t="n">
         <v>1</v>
       </c>
       <c r="C84" s="8" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="D84" s="8" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="E84" s="8" t="s">
         <v>23</v>
@@ -3529,7 +3526,7 @@
         <v>23</v>
       </c>
       <c r="G84" s="8" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="H84" s="9"/>
       <c r="I84" s="10" t="n">
@@ -3541,16 +3538,16 @@
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="6" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B85" s="7" t="n">
         <v>1</v>
       </c>
       <c r="C85" s="8" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="D85" s="8" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="E85" s="8" t="s">
         <v>23</v>
@@ -3559,7 +3556,7 @@
         <v>23</v>
       </c>
       <c r="G85" s="8" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="H85" s="9"/>
       <c r="I85" s="10" t="n">
@@ -3570,28 +3567,64 @@
       <c r="K85" s="12"/>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G86" s="13" t="s">
+      <c r="A86" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="B86" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C86" s="8" t="s">
+        <v>231</v>
+      </c>
+      <c r="D86" s="8" t="s">
+        <v>232</v>
+      </c>
+      <c r="E86" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F86" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="G86" s="8" t="s">
+        <v>233</v>
+      </c>
+      <c r="H86" s="9"/>
+      <c r="I86" s="10" t="n">
+        <f aca="false">B86*H86</f>
+        <v>0</v>
+      </c>
+      <c r="J86" s="11"/>
+      <c r="K86" s="12"/>
+    </row>
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="6" t="n">
+        <v>61</v>
+      </c>
+      <c r="B87" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C87" s="8" t="s">
         <v>234</v>
       </c>
-      <c r="I86" s="14" t="n">
-        <f aca="false">SUM(I78:I85)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="5" t="s">
+      <c r="D87" s="8" t="s">
         <v>235</v>
       </c>
-      <c r="B87" s="5"/>
-      <c r="C87" s="5"/>
-      <c r="D87" s="5"/>
-      <c r="E87" s="5"/>
-      <c r="F87" s="5"/>
-      <c r="G87" s="5"/>
-      <c r="H87" s="5"/>
-      <c r="I87" s="5"/>
-      <c r="J87" s="5"/>
-      <c r="K87" s="5"/>
+      <c r="E87" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F87" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="G87" s="8" t="s">
+        <v>236</v>
+      </c>
+      <c r="H87" s="9"/>
+      <c r="I87" s="10" t="n">
+        <f aca="false">B87*H87</f>
+        <v>0</v>
+      </c>
+      <c r="J87" s="11"/>
+      <c r="K87" s="12"/>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="6" t="n">
@@ -3601,19 +3634,19 @@
         <v>1</v>
       </c>
       <c r="C88" s="8" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D88" s="8" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E88" s="8" t="s">
         <v>23</v>
       </c>
       <c r="F88" s="6" t="s">
-        <v>61</v>
+        <v>23</v>
       </c>
       <c r="G88" s="8" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="H88" s="9"/>
       <c r="I88" s="10" t="n">
@@ -3623,7 +3656,7 @@
       <c r="J88" s="11"/>
       <c r="K88" s="12"/>
     </row>
-    <row r="89" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="6" t="n">
         <v>63</v>
       </c>
@@ -3640,7 +3673,7 @@
         <v>23</v>
       </c>
       <c r="F89" s="6" t="s">
-        <v>61</v>
+        <v>23</v>
       </c>
       <c r="G89" s="8" t="s">
         <v>241</v>
@@ -3653,7 +3686,7 @@
       <c r="J89" s="11"/>
       <c r="K89" s="12"/>
     </row>
-    <row r="90" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="6" t="n">
         <v>64</v>
       </c>
@@ -3670,7 +3703,7 @@
         <v>23</v>
       </c>
       <c r="F90" s="6" t="s">
-        <v>61</v>
+        <v>23</v>
       </c>
       <c r="G90" s="8" t="s">
         <v>244</v>
@@ -3684,74 +3717,188 @@
       <c r="K90" s="12"/>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="6" t="n">
+      <c r="G91" s="13" t="s">
+        <v>245</v>
+      </c>
+      <c r="I91" s="14" t="n">
+        <f aca="false">SUM(I83:I90)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="B92" s="5"/>
+      <c r="C92" s="5"/>
+      <c r="D92" s="5"/>
+      <c r="E92" s="5"/>
+      <c r="F92" s="5"/>
+      <c r="G92" s="5"/>
+      <c r="H92" s="5"/>
+      <c r="I92" s="5"/>
+      <c r="J92" s="5"/>
+      <c r="K92" s="5"/>
+    </row>
+    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="6" t="n">
         <v>65</v>
       </c>
-      <c r="B91" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C91" s="8" t="s">
-        <v>245</v>
-      </c>
-      <c r="D91" s="8" t="s">
-        <v>246</v>
-      </c>
-      <c r="E91" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="F91" s="6" t="s">
+      <c r="B93" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C93" s="8" t="s">
+        <v>247</v>
+      </c>
+      <c r="D93" s="8" t="s">
+        <v>248</v>
+      </c>
+      <c r="E93" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F93" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="G93" s="8" t="s">
+        <v>249</v>
+      </c>
+      <c r="H93" s="9"/>
+      <c r="I93" s="10" t="n">
+        <f aca="false">B93*H93</f>
+        <v>0</v>
+      </c>
+      <c r="J93" s="11"/>
+      <c r="K93" s="12"/>
+    </row>
+    <row r="94" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="6" t="n">
+        <v>66</v>
+      </c>
+      <c r="B94" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C94" s="8" t="s">
+        <v>250</v>
+      </c>
+      <c r="D94" s="8" t="s">
+        <v>251</v>
+      </c>
+      <c r="E94" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F94" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="G94" s="8" t="s">
+        <v>252</v>
+      </c>
+      <c r="H94" s="9"/>
+      <c r="I94" s="10" t="n">
+        <f aca="false">B94*H94</f>
+        <v>0</v>
+      </c>
+      <c r="J94" s="11"/>
+      <c r="K94" s="12"/>
+    </row>
+    <row r="95" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A95" s="6" t="n">
+        <v>67</v>
+      </c>
+      <c r="B95" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C95" s="8" t="s">
+        <v>253</v>
+      </c>
+      <c r="D95" s="8" t="s">
+        <v>254</v>
+      </c>
+      <c r="E95" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F95" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="G95" s="8" t="s">
+        <v>255</v>
+      </c>
+      <c r="H95" s="9"/>
+      <c r="I95" s="10" t="n">
+        <f aca="false">B95*H95</f>
+        <v>0</v>
+      </c>
+      <c r="J95" s="11"/>
+      <c r="K95" s="12"/>
+    </row>
+    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A96" s="6" t="n">
+        <v>68</v>
+      </c>
+      <c r="B96" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C96" s="8" t="s">
+        <v>256</v>
+      </c>
+      <c r="D96" s="8" t="s">
+        <v>257</v>
+      </c>
+      <c r="E96" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F96" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="G91" s="8" t="s">
-        <v>247</v>
-      </c>
-      <c r="H91" s="9"/>
-      <c r="I91" s="10" t="n">
-        <f aca="false">B91*H91</f>
-        <v>0</v>
-      </c>
-      <c r="J91" s="11"/>
-      <c r="K91" s="12"/>
-    </row>
-    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G92" s="13" t="s">
-        <v>248</v>
-      </c>
-      <c r="I92" s="14" t="n">
-        <f aca="false">SUM(I88:I91)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G94" s="15" t="s">
-        <v>249</v>
-      </c>
-      <c r="I94" s="16" t="n">
-        <f aca="false">I13+I19+I32+I38+I48+I56+I65+I71+I76+I86+I92</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G95" s="17" t="s">
-        <v>250</v>
-      </c>
-      <c r="I95" s="18" t="n">
-        <f aca="false">COUNTIF(B6:B86,"&gt;0")-COUNTIF(K6:K86,"Y")</f>
-        <v>58</v>
-      </c>
+      <c r="G96" s="8" t="s">
+        <v>258</v>
+      </c>
+      <c r="H96" s="9"/>
+      <c r="I96" s="10" t="n">
+        <f aca="false">B96*H96</f>
+        <v>0</v>
+      </c>
+      <c r="J96" s="11"/>
+      <c r="K96" s="12"/>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="19" t="s">
-        <v>251</v>
+      <c r="G97" s="13" t="s">
+        <v>259</v>
+      </c>
+      <c r="I97" s="14" t="n">
+        <f aca="false">SUM(I93:I96)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G99" s="15" t="s">
+        <v>260</v>
+      </c>
+      <c r="I99" s="16" t="n">
+        <f aca="false">I13+I19+I32+I38+I48+I56+I65+I71+I76+I81+I91+I97</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G100" s="17" t="s">
+        <v>261</v>
+      </c>
+      <c r="I100" s="18" t="n">
+        <f aca="false">COUNTIF(B6:B91,"&gt;0")-COUNTIF(K6:K91,"Y")</f>
+        <v>61</v>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A102" s="19" t="s">
+        <v>262</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A5:K92"/>
+  <autoFilter ref="A5:K97"/>
   <mergeCells count="1">
     <mergeCell ref="A3:K3"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="K7:K12 K15:K18 K21:K31 K34:K37 K40:K47 K50:K55 K58:K64 K67:K70 K73:K75 K78:K85 K88:K91" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="K7:K12 K15:K18 K21:K31 K34:K37 K40:K47 K50:K55 K58:K64 K67:K70 K73:K75 K78:K80 K83:K90 K93:K96" type="list">
       <formula1>"Y,N"</formula1>
       <formula2>0</formula2>
     </dataValidation>

--- a/bobcat-dash-BOM.xlsx
+++ b/bobcat-dash-BOM.xlsx
@@ -10,7 +10,7 @@
     <sheet name="BOM" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'BOM'!$A$5:$K$99</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'BOM'!$A$5:$K$100</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'BOM'!$5:$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -541,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K104"/>
+  <dimension ref="A1:K105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3561,7 +3561,7 @@
       </c>
       <c r="G92" s="8" t="inlineStr">
         <is>
-          <t>Mount Pi and boards</t>
+          <t>Mount the Pi and the plug-in modules</t>
         </is>
       </c>
       <c r="H92" s="9" t="n"/>
@@ -3573,72 +3573,72 @@
       <c r="K92" s="12" t="n"/>
     </row>
     <row r="93">
-      <c r="G93" s="13" t="inlineStr">
+      <c r="A93" s="6" t="n">
+        <v>67</v>
+      </c>
+      <c r="B93" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="C93" s="8" t="inlineStr">
+        <is>
+          <t>M3 standoff + screws</t>
+        </is>
+      </c>
+      <c r="D93" s="8" t="inlineStr">
+        <is>
+          <t>10 mm or taller, all the same height</t>
+        </is>
+      </c>
+      <c r="E93" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F93" s="6" t="inlineStr">
+        <is>
+          <t>Board README</t>
+        </is>
+      </c>
+      <c r="G93" s="8" t="inlineStr">
+        <is>
+          <t>Breakout board mounting: 4 corners, 4 mid-sides, 1 centre (drilling template)</t>
+        </is>
+      </c>
+      <c r="H93" s="9" t="n"/>
+      <c r="I93" s="10">
+        <f>B93*H93</f>
+        <v/>
+      </c>
+      <c r="J93" s="11" t="n"/>
+      <c r="K93" s="12" t="n"/>
+    </row>
+    <row r="94">
+      <c r="G94" s="13" t="inlineStr">
         <is>
           <t>Subtotal — Wiring + Enclosure</t>
         </is>
       </c>
-      <c r="I93" s="14">
-        <f>SUM(I85:I92)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="5" t="inlineStr">
+      <c r="I94" s="14">
+        <f>SUM(I85:I93)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="5" t="inlineStr">
         <is>
           <t>EXISTING MACHINE PARTS (reuse, check they work)</t>
         </is>
       </c>
-      <c r="B94" s="5" t="n"/>
-      <c r="C94" s="5" t="n"/>
-      <c r="D94" s="5" t="n"/>
-      <c r="E94" s="5" t="n"/>
-      <c r="F94" s="5" t="n"/>
-      <c r="G94" s="5" t="n"/>
-      <c r="H94" s="5" t="n"/>
-      <c r="I94" s="5" t="n"/>
-      <c r="J94" s="5" t="n"/>
-      <c r="K94" s="5" t="n"/>
-    </row>
-    <row r="95">
-      <c r="A95" s="6" t="n">
-        <v>67</v>
-      </c>
-      <c r="B95" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C95" s="8" t="inlineStr">
-        <is>
-          <t>Oil pressure switch</t>
-        </is>
-      </c>
-      <c r="D95" s="8" t="inlineStr">
-        <is>
-          <t>Original, closes on low pressure</t>
-        </is>
-      </c>
-      <c r="E95" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F95" s="6" t="inlineStr">
-        <is>
-          <t>Sch. 5</t>
-        </is>
-      </c>
-      <c r="G95" s="8" t="inlineStr">
-        <is>
-          <t>GPIO 22 via optocoupler</t>
-        </is>
-      </c>
-      <c r="H95" s="9" t="n"/>
-      <c r="I95" s="10">
-        <f>B95*H95</f>
-        <v/>
-      </c>
-      <c r="J95" s="11" t="n"/>
-      <c r="K95" s="12" t="n"/>
+      <c r="B95" s="5" t="n"/>
+      <c r="C95" s="5" t="n"/>
+      <c r="D95" s="5" t="n"/>
+      <c r="E95" s="5" t="n"/>
+      <c r="F95" s="5" t="n"/>
+      <c r="G95" s="5" t="n"/>
+      <c r="H95" s="5" t="n"/>
+      <c r="I95" s="5" t="n"/>
+      <c r="J95" s="5" t="n"/>
+      <c r="K95" s="5" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="6" t="n">
@@ -3649,12 +3649,12 @@
       </c>
       <c r="C96" s="8" t="inlineStr">
         <is>
-          <t>Hydraulic filter bypass switch</t>
+          <t>Oil pressure switch</t>
         </is>
       </c>
       <c r="D96" s="8" t="inlineStr">
         <is>
-          <t>Original, closes on bypass</t>
+          <t>Original, closes on low pressure</t>
         </is>
       </c>
       <c r="E96" s="8" t="inlineStr">
@@ -3669,7 +3669,7 @@
       </c>
       <c r="G96" s="8" t="inlineStr">
         <is>
-          <t>ADS1115 A2, monitored (4.7k EOL resistor at the switch)</t>
+          <t>GPIO 22 via optocoupler</t>
         </is>
       </c>
       <c r="H96" s="9" t="n"/>
@@ -3689,12 +3689,12 @@
       </c>
       <c r="C97" s="8" t="inlineStr">
         <is>
-          <t>Hydraulic oil temp switch</t>
+          <t>Hydraulic filter bypass switch</t>
         </is>
       </c>
       <c r="D97" s="8" t="inlineStr">
         <is>
-          <t>Original, closes when hot</t>
+          <t>Original, closes on bypass</t>
         </is>
       </c>
       <c r="E97" s="8" t="inlineStr">
@@ -3709,7 +3709,7 @@
       </c>
       <c r="G97" s="8" t="inlineStr">
         <is>
-          <t>ADS1115 A3, monitored (4.7k EOL resistor at the switch)</t>
+          <t>ADS1115 A2, monitored (4.7k EOL resistor at the switch)</t>
         </is>
       </c>
       <c r="H97" s="9" t="n"/>
@@ -3729,12 +3729,12 @@
       </c>
       <c r="C98" s="8" t="inlineStr">
         <is>
-          <t>Fuel sender</t>
+          <t>Hydraulic oil temp switch</t>
         </is>
       </c>
       <c r="D98" s="8" t="inlineStr">
         <is>
-          <t>Original, in tank</t>
+          <t>Original, closes when hot</t>
         </is>
       </c>
       <c r="E98" s="8" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="F98" s="6" t="inlineStr">
         <is>
-          <t>Sch. 4</t>
+          <t>Sch. 5</t>
         </is>
       </c>
       <c r="G98" s="8" t="inlineStr">
         <is>
-          <t>Calibrate with dash.py --calibrate</t>
+          <t>ADS1115 A3, monitored (4.7k EOL resistor at the switch)</t>
         </is>
       </c>
       <c r="H98" s="9" t="n"/>
@@ -3761,52 +3761,92 @@
       <c r="K98" s="12" t="n"/>
     </row>
     <row r="99">
-      <c r="G99" s="13" t="inlineStr">
+      <c r="A99" s="6" t="n">
+        <v>71</v>
+      </c>
+      <c r="B99" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C99" s="8" t="inlineStr">
+        <is>
+          <t>Fuel sender</t>
+        </is>
+      </c>
+      <c r="D99" s="8" t="inlineStr">
+        <is>
+          <t>Original, in tank</t>
+        </is>
+      </c>
+      <c r="E99" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F99" s="6" t="inlineStr">
+        <is>
+          <t>Sch. 4</t>
+        </is>
+      </c>
+      <c r="G99" s="8" t="inlineStr">
+        <is>
+          <t>Calibrate with dash.py --calibrate</t>
+        </is>
+      </c>
+      <c r="H99" s="9" t="n"/>
+      <c r="I99" s="10">
+        <f>B99*H99</f>
+        <v/>
+      </c>
+      <c r="J99" s="11" t="n"/>
+      <c r="K99" s="12" t="n"/>
+    </row>
+    <row r="100">
+      <c r="G100" s="13" t="inlineStr">
         <is>
           <t>Subtotal — Existing Machine Parts</t>
         </is>
       </c>
-      <c r="I99" s="14">
-        <f>SUM(I95:I98)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="101">
-      <c r="G101" s="15" t="inlineStr">
+      <c r="I100" s="14">
+        <f>SUM(I96:I99)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="102">
+      <c r="G102" s="15" t="inlineStr">
         <is>
           <t>TOTAL (all sections)</t>
         </is>
       </c>
-      <c r="I101" s="16">
-        <f>I13+I19+I33+I39+I50+I58+I67+I73+I78+I83+I93+I99</f>
-        <v/>
-      </c>
-    </row>
-    <row r="102">
-      <c r="G102" s="17" t="inlineStr">
+      <c r="I102" s="16">
+        <f>I13+I19+I33+I39+I50+I58+I67+I73+I78+I83+I94+I100</f>
+        <v/>
+      </c>
+    </row>
+    <row r="103">
+      <c r="G103" s="17" t="inlineStr">
         <is>
           <t>Items still to order (excl. existing parts)</t>
         </is>
       </c>
-      <c r="I102" s="18">
-        <f>COUNTIF(B6:B93,"&gt;0")-COUNTIF(K6:K93,"Y")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="19" t="inlineStr">
+      <c r="I103" s="18">
+        <f>COUNTIF(B6:B94,"&gt;0")-COUNTIF(K6:K94,"Y")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="19" t="inlineStr">
         <is>
           <t>Notes: Qty in blue = quantity per machine. Existing machine parts usually cost $0 unless one needs replacing. Prices are left blank on purpose. Enter what you actually pay.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A5:K99"/>
+  <autoFilter ref="A5:K100"/>
   <mergeCells count="1">
     <mergeCell ref="A3:K3"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="K7 K8 K9 K10 K11 K12 K15 K16 K17 K18 K21 K22 K23 K24 K25 K26 K27 K28 K29 K30 K31 K32 K35 K36 K37 K38 K41 K42 K43 K44 K45 K46 K47 K48 K49 K52 K53 K54 K55 K56 K57 K60 K61 K62 K63 K64 K65 K66 K69 K70 K71 K72 K75 K76 K77 K80 K81 K82 K85 K86 K87 K88 K89 K90 K91 K92 K95 K96 K97 K98" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K7 K8 K9 K10 K11 K12 K15 K16 K17 K18 K21 K22 K23 K24 K25 K26 K27 K28 K29 K30 K31 K32 K35 K36 K37 K38 K41 K42 K43 K44 K45 K46 K47 K48 K49 K52 K53 K54 K55 K56 K57 K60 K61 K62 K63 K64 K65 K66 K69 K70 K71 K72 K75 K76 K77 K80 K81 K82 K85 K86 K87 K88 K89 K90 K91 K92 K93 K96 K97 K98 K99" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Y,N"</formula1>
     </dataValidation>
   </dataValidations>

--- a/bobcat-dash-BOM.xlsx
+++ b/bobcat-dash-BOM.xlsx
@@ -10,7 +10,7 @@
     <sheet name="BOM" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'BOM'!$A$5:$K$100</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'BOM'!$A$5:$K$108</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'BOM'!$5:$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -541,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K105"/>
+  <dimension ref="A1:K113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="D52" s="8" t="inlineStr">
         <is>
-          <t>162 × 159 mm (rev 2.8), 2 layers, 1.6 mm, 1 oz</t>
+          <t>162 × 159 mm (rev 2.9), 2 layers, 1.6 mm, 1 oz</t>
         </is>
       </c>
       <c r="E52" s="8" t="inlineStr">
@@ -3077,63 +3077,115 @@
       <c r="K77" s="12" t="n"/>
     </row>
     <row r="78">
-      <c r="G78" s="13" t="inlineStr">
-        <is>
-          <t>Subtotal — Temperature: Readme, Temperatures</t>
-        </is>
-      </c>
-      <c r="I78" s="14">
-        <f>SUM(I75:I77)</f>
-        <v/>
-      </c>
+      <c r="A78" s="6" t="n">
+        <v>56</v>
+      </c>
+      <c r="B78" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C78" s="8" t="inlineStr">
+        <is>
+          <t>Micro-Fit 3.0 receptacle housing</t>
+        </is>
+      </c>
+      <c r="D78" s="8" t="inlineStr">
+        <is>
+          <t>8-position, single row, latching</t>
+        </is>
+      </c>
+      <c r="E78" s="8" t="inlineStr">
+        <is>
+          <t>Molex 43645-0800</t>
+        </is>
+      </c>
+      <c r="F78" s="6" t="inlineStr">
+        <is>
+          <t>Board README: BUTTON POD</t>
+        </is>
+      </c>
+      <c r="G78" s="8" t="inlineStr">
+        <is>
+          <t>Plugs into the board's POD header J17 (43650-0815)</t>
+        </is>
+      </c>
+      <c r="H78" s="9" t="n"/>
+      <c r="I78" s="10">
+        <f>B78*H78</f>
+        <v/>
+      </c>
+      <c r="J78" s="11" t="n"/>
+      <c r="K78" s="12" t="n"/>
     </row>
     <row r="79">
-      <c r="A79" s="5" t="inlineStr">
-        <is>
-          <t>CHARGING: Delco 10SI 3-wire alternator (wiring-schematic.jpg, section 7)</t>
-        </is>
-      </c>
-      <c r="B79" s="5" t="n"/>
-      <c r="C79" s="5" t="n"/>
-      <c r="D79" s="5" t="n"/>
-      <c r="E79" s="5" t="n"/>
-      <c r="F79" s="5" t="n"/>
-      <c r="G79" s="5" t="n"/>
-      <c r="H79" s="5" t="n"/>
-      <c r="I79" s="5" t="n"/>
-      <c r="J79" s="5" t="n"/>
-      <c r="K79" s="5" t="n"/>
+      <c r="A79" s="6" t="n">
+        <v>57</v>
+      </c>
+      <c r="B79" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="C79" s="8" t="inlineStr">
+        <is>
+          <t>Micro-Fit 3.0 crimp pins</t>
+        </is>
+      </c>
+      <c r="D79" s="8" t="inlineStr">
+        <is>
+          <t>Female, 20-24 AWG</t>
+        </is>
+      </c>
+      <c r="E79" s="8" t="inlineStr">
+        <is>
+          <t>Molex 43030-0007</t>
+        </is>
+      </c>
+      <c r="F79" s="6" t="inlineStr">
+        <is>
+          <t>Board README: BUTTON POD</t>
+        </is>
+      </c>
+      <c r="G79" s="8" t="inlineStr">
+        <is>
+          <t>8-core cable, board to the pod (buttons, SILENCE, GND, fan)</t>
+        </is>
+      </c>
+      <c r="H79" s="9" t="n"/>
+      <c r="I79" s="10">
+        <f>B79*H79</f>
+        <v/>
+      </c>
+      <c r="J79" s="11" t="n"/>
+      <c r="K79" s="12" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="6" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B80" s="7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C80" s="8" t="inlineStr">
         <is>
-          <t>Rectifier diode</t>
+          <t>Pushbutton head, black</t>
         </is>
       </c>
       <c r="D80" s="8" t="inlineStr">
         <is>
-          <t>1N4001, 1 A 50 V</t>
+          <t>Eaton M22, 22 mm, momentary</t>
         </is>
       </c>
       <c r="E80" s="8" t="inlineStr">
         <is>
-          <t>1N4001</t>
+          <t>Eaton M22-D-S (flat-style head)</t>
         </is>
       </c>
       <c r="F80" s="6" t="inlineStr">
         <is>
-          <t>Sch. 7</t>
+          <t>enclosure/button-pod</t>
         </is>
       </c>
       <c r="G80" s="8" t="inlineStr">
         <is>
-          <t>In the terminal 1 (excite) wire, band toward the alternator: stops the running alternator back-feeding the key circuit (engine run-on, dash never sees key-off)</t>
+          <t>LEFT, RIGHT, OK, BACK</t>
         </is>
       </c>
       <c r="H80" s="9" t="n"/>
@@ -3146,34 +3198,34 @@
     </row>
     <row r="81">
       <c r="A81" s="6" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B81" s="7" t="n">
         <v>1</v>
       </c>
       <c r="C81" s="8" t="inlineStr">
         <is>
-          <t>Resistor 47 Ω</t>
+          <t>Pushbutton head, red mushroom</t>
         </is>
       </c>
       <c r="D81" s="8" t="inlineStr">
         <is>
-          <t>5 W wirewound</t>
+          <t>Eaton M22, 22 mm, momentary</t>
         </is>
       </c>
       <c r="E81" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Eaton M22-DP-R</t>
         </is>
       </c>
       <c r="F81" s="6" t="inlineStr">
         <is>
-          <t>Sch. 7</t>
+          <t>enclosure/button-pod</t>
         </is>
       </c>
       <c r="G81" s="8" t="inlineStr">
         <is>
-          <t>In series with the diode: ~0.25 A with the key on and the engine stopped, like the charge lamp it replaces. Use the alternator maker's value if they give one</t>
+          <t>ALARM SILENCE</t>
         </is>
       </c>
       <c r="H81" s="9" t="n"/>
@@ -3186,34 +3238,34 @@
     </row>
     <row r="82">
       <c r="A82" s="6" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B82" s="7" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C82" s="8" t="inlineStr">
         <is>
-          <t>Fusible link or circuit breaker</t>
+          <t>Fixing adapter</t>
         </is>
       </c>
       <c r="D82" s="8" t="inlineStr">
         <is>
-          <t>Rated for the alternator (e.g. 60 A)</t>
+          <t>Eaton M22</t>
         </is>
       </c>
       <c r="E82" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Eaton M22-A</t>
         </is>
       </c>
       <c r="F82" s="6" t="inlineStr">
         <is>
-          <t>Sch. 7</t>
+          <t>enclosure/button-pod</t>
         </is>
       </c>
       <c r="G82" s="8" t="inlineStr">
         <is>
-          <t>On the BAT stud wire, near the battery end. 8 AWG wire (10 AWG for 45 A units)</t>
+          <t>One per button</t>
         </is>
       </c>
       <c r="H82" s="9" t="n"/>
@@ -3225,63 +3277,115 @@
       <c r="K82" s="12" t="n"/>
     </row>
     <row r="83">
-      <c r="G83" s="13" t="inlineStr">
-        <is>
-          <t>Subtotal — Charging: Delco 10Si 3-Wire Alternator</t>
-        </is>
-      </c>
-      <c r="I83" s="14">
-        <f>SUM(I80:I82)</f>
-        <v/>
-      </c>
+      <c r="A83" s="6" t="n">
+        <v>61</v>
+      </c>
+      <c r="B83" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C83" s="8" t="inlineStr">
+        <is>
+          <t>Contact block, 1 NO</t>
+        </is>
+      </c>
+      <c r="D83" s="8" t="inlineStr">
+        <is>
+          <t>Eaton M22</t>
+        </is>
+      </c>
+      <c r="E83" s="8" t="inlineStr">
+        <is>
+          <t>Eaton M22-K10</t>
+        </is>
+      </c>
+      <c r="F83" s="6" t="inlineStr">
+        <is>
+          <t>enclosure/button-pod</t>
+        </is>
+      </c>
+      <c r="G83" s="8" t="inlineStr">
+        <is>
+          <t>One per button</t>
+        </is>
+      </c>
+      <c r="H83" s="9" t="n"/>
+      <c r="I83" s="10">
+        <f>B83*H83</f>
+        <v/>
+      </c>
+      <c r="J83" s="11" t="n"/>
+      <c r="K83" s="12" t="n"/>
     </row>
     <row r="84">
-      <c r="A84" s="5" t="inlineStr">
-        <is>
-          <t>WIRING + ENCLOSURE</t>
-        </is>
-      </c>
-      <c r="B84" s="5" t="n"/>
-      <c r="C84" s="5" t="n"/>
-      <c r="D84" s="5" t="n"/>
-      <c r="E84" s="5" t="n"/>
-      <c r="F84" s="5" t="n"/>
-      <c r="G84" s="5" t="n"/>
-      <c r="H84" s="5" t="n"/>
-      <c r="I84" s="5" t="n"/>
-      <c r="J84" s="5" t="n"/>
-      <c r="K84" s="5" t="n"/>
+      <c r="A84" s="6" t="n">
+        <v>62</v>
+      </c>
+      <c r="B84" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C84" s="8" t="inlineStr">
+        <is>
+          <t>Exhaust fan</t>
+        </is>
+      </c>
+      <c r="D84" s="8" t="inlineStr">
+        <is>
+          <t>40 x 40 x 10 mm, 12 V</t>
+        </is>
+      </c>
+      <c r="E84" s="8" t="inlineStr">
+        <is>
+          <t>any (two-wire)</t>
+        </is>
+      </c>
+      <c r="F84" s="6" t="inlineStr">
+        <is>
+          <t>enclosure/button-pod</t>
+        </is>
+      </c>
+      <c r="G84" s="8" t="inlineStr">
+        <is>
+          <t>Back wall of the pod; switched by the board (Q5)</t>
+        </is>
+      </c>
+      <c r="H84" s="9" t="n"/>
+      <c r="I84" s="10">
+        <f>B84*H84</f>
+        <v/>
+      </c>
+      <c r="J84" s="11" t="n"/>
+      <c r="K84" s="12" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="6" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="B85" s="7" t="n">
         <v>1</v>
       </c>
       <c r="C85" s="8" t="inlineStr">
         <is>
-          <t>Enclosure</t>
+          <t>Cable gland</t>
         </is>
       </c>
       <c r="D85" s="8" t="inlineStr">
         <is>
-          <t>IP65+, fits Pi + interface boards</t>
+          <t>M20, for the HDMI cable</t>
         </is>
       </c>
       <c r="E85" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>nylon or nickel-brass</t>
         </is>
       </c>
       <c r="F85" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>enclosure/button-pod</t>
         </is>
       </c>
       <c r="G85" s="8" t="inlineStr">
         <is>
-          <t>Vibration-mount it</t>
+          <t>Back wall of the pod</t>
         </is>
       </c>
       <c r="H85" s="9" t="n"/>
@@ -3293,115 +3397,63 @@
       <c r="K85" s="12" t="n"/>
     </row>
     <row r="86">
-      <c r="A86" s="6" t="n">
-        <v>60</v>
-      </c>
-      <c r="B86" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C86" s="8" t="inlineStr">
-        <is>
-          <t>Prototype board</t>
-        </is>
-      </c>
-      <c r="D86" s="8" t="inlineStr">
-        <is>
-          <t>Perfboard / stripboard</t>
-        </is>
-      </c>
-      <c r="E86" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F86" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G86" s="8" t="inlineStr">
-        <is>
-          <t>Only if hand-wiring instead of the breakout board</t>
-        </is>
-      </c>
-      <c r="H86" s="9" t="n"/>
-      <c r="I86" s="10">
-        <f>B86*H86</f>
-        <v/>
-      </c>
-      <c r="J86" s="11" t="n"/>
-      <c r="K86" s="12" t="n"/>
+      <c r="G86" s="13" t="inlineStr">
+        <is>
+          <t>Subtotal — Temperature: Readme, Temperatures</t>
+        </is>
+      </c>
+      <c r="I86" s="14">
+        <f>SUM(I75:I85)</f>
+        <v/>
+      </c>
     </row>
     <row r="87">
-      <c r="A87" s="6" t="n">
-        <v>61</v>
-      </c>
-      <c r="B87" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C87" s="8" t="inlineStr">
-        <is>
-          <t>Automotive wire</t>
-        </is>
-      </c>
-      <c r="D87" s="8" t="inlineStr">
-        <is>
-          <t>18 AWG TXL/GXL, several colors</t>
-        </is>
-      </c>
-      <c r="E87" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F87" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G87" s="8" t="inlineStr">
-        <is>
-          <t>Lot</t>
-        </is>
-      </c>
-      <c r="H87" s="9" t="n"/>
-      <c r="I87" s="10">
-        <f>B87*H87</f>
-        <v/>
-      </c>
-      <c r="J87" s="11" t="n"/>
-      <c r="K87" s="12" t="n"/>
+      <c r="A87" s="5" t="inlineStr">
+        <is>
+          <t>CHARGING: Delco 10SI 3-wire alternator (wiring-schematic.jpg, section 7)</t>
+        </is>
+      </c>
+      <c r="B87" s="5" t="n"/>
+      <c r="C87" s="5" t="n"/>
+      <c r="D87" s="5" t="n"/>
+      <c r="E87" s="5" t="n"/>
+      <c r="F87" s="5" t="n"/>
+      <c r="G87" s="5" t="n"/>
+      <c r="H87" s="5" t="n"/>
+      <c r="I87" s="5" t="n"/>
+      <c r="J87" s="5" t="n"/>
+      <c r="K87" s="5" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="6" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B88" s="7" t="n">
         <v>1</v>
       </c>
       <c r="C88" s="8" t="inlineStr">
         <is>
-          <t>Sealed connectors</t>
+          <t>Rectifier diode</t>
         </is>
       </c>
       <c r="D88" s="8" t="inlineStr">
         <is>
-          <t>Deutsch DT or Weatherpack assortment</t>
+          <t>1N4001, 1 A 50 V</t>
         </is>
       </c>
       <c r="E88" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1N4001</t>
         </is>
       </c>
       <c r="F88" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Sch. 7</t>
         </is>
       </c>
       <c r="G88" s="8" t="inlineStr">
         <is>
-          <t>Avoid loose Dupont jumpers on the machine</t>
+          <t>In the terminal 1 (excite) wire, band toward the alternator: stops the running alternator back-feeding the key circuit (engine run-on, dash never sees key-off)</t>
         </is>
       </c>
       <c r="H88" s="9" t="n"/>
@@ -3414,19 +3466,19 @@
     </row>
     <row r="89">
       <c r="A89" s="6" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B89" s="7" t="n">
         <v>1</v>
       </c>
       <c r="C89" s="8" t="inlineStr">
         <is>
-          <t>Screw terminal blocks</t>
+          <t>Resistor 47 Ω</t>
         </is>
       </c>
       <c r="D89" s="8" t="inlineStr">
         <is>
-          <t>PCB 5 mm pitch assortment</t>
+          <t>5 W wirewound</t>
         </is>
       </c>
       <c r="E89" s="8" t="inlineStr">
@@ -3436,12 +3488,12 @@
       </c>
       <c r="F89" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Sch. 7</t>
         </is>
       </c>
       <c r="G89" s="8" t="inlineStr">
         <is>
-          <t>Field wiring into the enclosure</t>
+          <t>In series with the diode: ~0.25 A with the key on and the engine stopped, like the charge lamp it replaces. Use the alternator maker's value if they give one</t>
         </is>
       </c>
       <c r="H89" s="9" t="n"/>
@@ -3454,19 +3506,19 @@
     </row>
     <row r="90">
       <c r="A90" s="6" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B90" s="7" t="n">
         <v>1</v>
       </c>
       <c r="C90" s="8" t="inlineStr">
         <is>
-          <t>Heat-shrink + terminals</t>
+          <t>Fusible link or circuit breaker</t>
         </is>
       </c>
       <c r="D90" s="8" t="inlineStr">
         <is>
-          <t>Assortment</t>
+          <t>Rated for the alternator (e.g. 60 A)</t>
         </is>
       </c>
       <c r="E90" s="8" t="inlineStr">
@@ -3476,12 +3528,12 @@
       </c>
       <c r="F90" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Sch. 7</t>
         </is>
       </c>
       <c r="G90" s="8" t="inlineStr">
         <is>
-          <t>Lot</t>
+          <t>On the BAT stud wire, near the battery end. 8 AWG wire (10 AWG for 45 A units)</t>
         </is>
       </c>
       <c r="H90" s="9" t="n"/>
@@ -3493,100 +3545,48 @@
       <c r="K90" s="12" t="n"/>
     </row>
     <row r="91">
-      <c r="A91" s="6" t="n">
-        <v>65</v>
-      </c>
-      <c r="B91" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C91" s="8" t="inlineStr">
-        <is>
-          <t>Display mount</t>
-        </is>
-      </c>
-      <c r="D91" s="8" t="inlineStr">
-        <is>
-          <t>RAM-style ball mount or bracket</t>
-        </is>
-      </c>
-      <c r="E91" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F91" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G91" s="8" t="inlineStr">
-        <is>
-          <t>With vibration damping</t>
-        </is>
-      </c>
-      <c r="H91" s="9" t="n"/>
-      <c r="I91" s="10">
-        <f>B91*H91</f>
-        <v/>
-      </c>
-      <c r="J91" s="11" t="n"/>
-      <c r="K91" s="12" t="n"/>
+      <c r="G91" s="13" t="inlineStr">
+        <is>
+          <t>Subtotal — Charging: Delco 10Si 3-Wire Alternator</t>
+        </is>
+      </c>
+      <c r="I91" s="14">
+        <f>SUM(I88:I90)</f>
+        <v/>
+      </c>
     </row>
     <row r="92">
-      <c r="A92" s="6" t="n">
-        <v>66</v>
-      </c>
-      <c r="B92" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C92" s="8" t="inlineStr">
-        <is>
-          <t>Standoffs</t>
-        </is>
-      </c>
-      <c r="D92" s="8" t="inlineStr">
-        <is>
-          <t>M2.5 nylon/brass set</t>
-        </is>
-      </c>
-      <c r="E92" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F92" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G92" s="8" t="inlineStr">
-        <is>
-          <t>Mount the Pi and the plug-in modules</t>
-        </is>
-      </c>
-      <c r="H92" s="9" t="n"/>
-      <c r="I92" s="10">
-        <f>B92*H92</f>
-        <v/>
-      </c>
-      <c r="J92" s="11" t="n"/>
-      <c r="K92" s="12" t="n"/>
+      <c r="A92" s="5" t="inlineStr">
+        <is>
+          <t>WIRING + ENCLOSURE</t>
+        </is>
+      </c>
+      <c r="B92" s="5" t="n"/>
+      <c r="C92" s="5" t="n"/>
+      <c r="D92" s="5" t="n"/>
+      <c r="E92" s="5" t="n"/>
+      <c r="F92" s="5" t="n"/>
+      <c r="G92" s="5" t="n"/>
+      <c r="H92" s="5" t="n"/>
+      <c r="I92" s="5" t="n"/>
+      <c r="J92" s="5" t="n"/>
+      <c r="K92" s="5" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="6" t="n">
         <v>67</v>
       </c>
       <c r="B93" s="7" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C93" s="8" t="inlineStr">
         <is>
-          <t>M3 standoff + screws</t>
+          <t>Enclosure</t>
         </is>
       </c>
       <c r="D93" s="8" t="inlineStr">
         <is>
-          <t>10 mm or taller, all the same height</t>
+          <t>IP65+, fits Pi + interface boards</t>
         </is>
       </c>
       <c r="E93" s="8" t="inlineStr">
@@ -3596,12 +3596,12 @@
       </c>
       <c r="F93" s="6" t="inlineStr">
         <is>
-          <t>Board README</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G93" s="8" t="inlineStr">
         <is>
-          <t>Breakout board mounting: 4 corners, 4 mid-sides, 1 centre (drilling template)</t>
+          <t>Vibration-mount it</t>
         </is>
       </c>
       <c r="H93" s="9" t="n"/>
@@ -3613,48 +3613,100 @@
       <c r="K93" s="12" t="n"/>
     </row>
     <row r="94">
-      <c r="G94" s="13" t="inlineStr">
-        <is>
-          <t>Subtotal — Wiring + Enclosure</t>
-        </is>
-      </c>
-      <c r="I94" s="14">
-        <f>SUM(I85:I93)</f>
-        <v/>
-      </c>
+      <c r="A94" s="6" t="n">
+        <v>68</v>
+      </c>
+      <c r="B94" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C94" s="8" t="inlineStr">
+        <is>
+          <t>Prototype board</t>
+        </is>
+      </c>
+      <c r="D94" s="8" t="inlineStr">
+        <is>
+          <t>Perfboard / stripboard</t>
+        </is>
+      </c>
+      <c r="E94" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F94" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G94" s="8" t="inlineStr">
+        <is>
+          <t>Only if hand-wiring instead of the breakout board</t>
+        </is>
+      </c>
+      <c r="H94" s="9" t="n"/>
+      <c r="I94" s="10">
+        <f>B94*H94</f>
+        <v/>
+      </c>
+      <c r="J94" s="11" t="n"/>
+      <c r="K94" s="12" t="n"/>
     </row>
     <row r="95">
-      <c r="A95" s="5" t="inlineStr">
-        <is>
-          <t>EXISTING MACHINE PARTS (reuse, check they work)</t>
-        </is>
-      </c>
-      <c r="B95" s="5" t="n"/>
-      <c r="C95" s="5" t="n"/>
-      <c r="D95" s="5" t="n"/>
-      <c r="E95" s="5" t="n"/>
-      <c r="F95" s="5" t="n"/>
-      <c r="G95" s="5" t="n"/>
-      <c r="H95" s="5" t="n"/>
-      <c r="I95" s="5" t="n"/>
-      <c r="J95" s="5" t="n"/>
-      <c r="K95" s="5" t="n"/>
+      <c r="A95" s="6" t="n">
+        <v>69</v>
+      </c>
+      <c r="B95" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C95" s="8" t="inlineStr">
+        <is>
+          <t>Automotive wire</t>
+        </is>
+      </c>
+      <c r="D95" s="8" t="inlineStr">
+        <is>
+          <t>18 AWG TXL/GXL, several colors</t>
+        </is>
+      </c>
+      <c r="E95" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F95" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G95" s="8" t="inlineStr">
+        <is>
+          <t>Lot</t>
+        </is>
+      </c>
+      <c r="H95" s="9" t="n"/>
+      <c r="I95" s="10">
+        <f>B95*H95</f>
+        <v/>
+      </c>
+      <c r="J95" s="11" t="n"/>
+      <c r="K95" s="12" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="6" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B96" s="7" t="n">
         <v>1</v>
       </c>
       <c r="C96" s="8" t="inlineStr">
         <is>
-          <t>Oil pressure switch</t>
+          <t>Sealed connectors</t>
         </is>
       </c>
       <c r="D96" s="8" t="inlineStr">
         <is>
-          <t>Original, closes on low pressure</t>
+          <t>Deutsch DT or Weatherpack assortment</t>
         </is>
       </c>
       <c r="E96" s="8" t="inlineStr">
@@ -3664,12 +3716,12 @@
       </c>
       <c r="F96" s="6" t="inlineStr">
         <is>
-          <t>Sch. 5</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G96" s="8" t="inlineStr">
         <is>
-          <t>GPIO 22 via optocoupler</t>
+          <t>Avoid loose Dupont jumpers on the machine</t>
         </is>
       </c>
       <c r="H96" s="9" t="n"/>
@@ -3682,19 +3734,19 @@
     </row>
     <row r="97">
       <c r="A97" s="6" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B97" s="7" t="n">
         <v>1</v>
       </c>
       <c r="C97" s="8" t="inlineStr">
         <is>
-          <t>Hydraulic filter bypass switch</t>
+          <t>Screw terminal blocks</t>
         </is>
       </c>
       <c r="D97" s="8" t="inlineStr">
         <is>
-          <t>Original, closes on bypass</t>
+          <t>PCB 5 mm pitch assortment</t>
         </is>
       </c>
       <c r="E97" s="8" t="inlineStr">
@@ -3704,12 +3756,12 @@
       </c>
       <c r="F97" s="6" t="inlineStr">
         <is>
-          <t>Sch. 5</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G97" s="8" t="inlineStr">
         <is>
-          <t>ADS1115 A2, monitored (4.7k EOL resistor at the switch)</t>
+          <t>Field wiring into the enclosure</t>
         </is>
       </c>
       <c r="H97" s="9" t="n"/>
@@ -3722,19 +3774,19 @@
     </row>
     <row r="98">
       <c r="A98" s="6" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B98" s="7" t="n">
         <v>1</v>
       </c>
       <c r="C98" s="8" t="inlineStr">
         <is>
-          <t>Hydraulic oil temp switch</t>
+          <t>Heat-shrink + terminals</t>
         </is>
       </c>
       <c r="D98" s="8" t="inlineStr">
         <is>
-          <t>Original, closes when hot</t>
+          <t>Assortment</t>
         </is>
       </c>
       <c r="E98" s="8" t="inlineStr">
@@ -3744,12 +3796,12 @@
       </c>
       <c r="F98" s="6" t="inlineStr">
         <is>
-          <t>Sch. 5</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G98" s="8" t="inlineStr">
         <is>
-          <t>ADS1115 A3, monitored (4.7k EOL resistor at the switch)</t>
+          <t>Lot</t>
         </is>
       </c>
       <c r="H98" s="9" t="n"/>
@@ -3762,19 +3814,19 @@
     </row>
     <row r="99">
       <c r="A99" s="6" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B99" s="7" t="n">
         <v>1</v>
       </c>
       <c r="C99" s="8" t="inlineStr">
         <is>
-          <t>Fuel sender</t>
+          <t>Display mount</t>
         </is>
       </c>
       <c r="D99" s="8" t="inlineStr">
         <is>
-          <t>Original, in tank</t>
+          <t>RAM-style ball mount or bracket</t>
         </is>
       </c>
       <c r="E99" s="8" t="inlineStr">
@@ -3784,12 +3836,12 @@
       </c>
       <c r="F99" s="6" t="inlineStr">
         <is>
-          <t>Sch. 4</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G99" s="8" t="inlineStr">
         <is>
-          <t>Calibrate with dash.py --calibrate</t>
+          <t>With vibration damping</t>
         </is>
       </c>
       <c r="H99" s="9" t="n"/>
@@ -3801,52 +3853,320 @@
       <c r="K99" s="12" t="n"/>
     </row>
     <row r="100">
-      <c r="G100" s="13" t="inlineStr">
+      <c r="A100" s="6" t="n">
+        <v>74</v>
+      </c>
+      <c r="B100" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C100" s="8" t="inlineStr">
+        <is>
+          <t>Standoffs</t>
+        </is>
+      </c>
+      <c r="D100" s="8" t="inlineStr">
+        <is>
+          <t>M2.5 nylon/brass set</t>
+        </is>
+      </c>
+      <c r="E100" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F100" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G100" s="8" t="inlineStr">
+        <is>
+          <t>Mount the Pi and the plug-in modules</t>
+        </is>
+      </c>
+      <c r="H100" s="9" t="n"/>
+      <c r="I100" s="10">
+        <f>B100*H100</f>
+        <v/>
+      </c>
+      <c r="J100" s="11" t="n"/>
+      <c r="K100" s="12" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="6" t="n">
+        <v>75</v>
+      </c>
+      <c r="B101" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="C101" s="8" t="inlineStr">
+        <is>
+          <t>M3 standoff + screws</t>
+        </is>
+      </c>
+      <c r="D101" s="8" t="inlineStr">
+        <is>
+          <t>10 mm or taller, all the same height</t>
+        </is>
+      </c>
+      <c r="E101" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F101" s="6" t="inlineStr">
+        <is>
+          <t>Board README</t>
+        </is>
+      </c>
+      <c r="G101" s="8" t="inlineStr">
+        <is>
+          <t>Breakout board mounting: 4 corners, 4 mid-sides, 1 centre (drilling template)</t>
+        </is>
+      </c>
+      <c r="H101" s="9" t="n"/>
+      <c r="I101" s="10">
+        <f>B101*H101</f>
+        <v/>
+      </c>
+      <c r="J101" s="11" t="n"/>
+      <c r="K101" s="12" t="n"/>
+    </row>
+    <row r="102">
+      <c r="G102" s="13" t="inlineStr">
+        <is>
+          <t>Subtotal — Wiring + Enclosure</t>
+        </is>
+      </c>
+      <c r="I102" s="14">
+        <f>SUM(I93:I101)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="5" t="inlineStr">
+        <is>
+          <t>EXISTING MACHINE PARTS (reuse, check they work)</t>
+        </is>
+      </c>
+      <c r="B103" s="5" t="n"/>
+      <c r="C103" s="5" t="n"/>
+      <c r="D103" s="5" t="n"/>
+      <c r="E103" s="5" t="n"/>
+      <c r="F103" s="5" t="n"/>
+      <c r="G103" s="5" t="n"/>
+      <c r="H103" s="5" t="n"/>
+      <c r="I103" s="5" t="n"/>
+      <c r="J103" s="5" t="n"/>
+      <c r="K103" s="5" t="n"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="6" t="n">
+        <v>76</v>
+      </c>
+      <c r="B104" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C104" s="8" t="inlineStr">
+        <is>
+          <t>Oil pressure switch</t>
+        </is>
+      </c>
+      <c r="D104" s="8" t="inlineStr">
+        <is>
+          <t>Original, closes on low pressure</t>
+        </is>
+      </c>
+      <c r="E104" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F104" s="6" t="inlineStr">
+        <is>
+          <t>Sch. 5</t>
+        </is>
+      </c>
+      <c r="G104" s="8" t="inlineStr">
+        <is>
+          <t>GPIO 22 via optocoupler</t>
+        </is>
+      </c>
+      <c r="H104" s="9" t="n"/>
+      <c r="I104" s="10">
+        <f>B104*H104</f>
+        <v/>
+      </c>
+      <c r="J104" s="11" t="n"/>
+      <c r="K104" s="12" t="n"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="6" t="n">
+        <v>77</v>
+      </c>
+      <c r="B105" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C105" s="8" t="inlineStr">
+        <is>
+          <t>Hydraulic filter bypass switch</t>
+        </is>
+      </c>
+      <c r="D105" s="8" t="inlineStr">
+        <is>
+          <t>Original, closes on bypass</t>
+        </is>
+      </c>
+      <c r="E105" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F105" s="6" t="inlineStr">
+        <is>
+          <t>Sch. 5</t>
+        </is>
+      </c>
+      <c r="G105" s="8" t="inlineStr">
+        <is>
+          <t>ADS1115 A2, monitored (4.7k EOL resistor at the switch)</t>
+        </is>
+      </c>
+      <c r="H105" s="9" t="n"/>
+      <c r="I105" s="10">
+        <f>B105*H105</f>
+        <v/>
+      </c>
+      <c r="J105" s="11" t="n"/>
+      <c r="K105" s="12" t="n"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="6" t="n">
+        <v>78</v>
+      </c>
+      <c r="B106" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C106" s="8" t="inlineStr">
+        <is>
+          <t>Hydraulic oil temp switch</t>
+        </is>
+      </c>
+      <c r="D106" s="8" t="inlineStr">
+        <is>
+          <t>Original, closes when hot</t>
+        </is>
+      </c>
+      <c r="E106" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F106" s="6" t="inlineStr">
+        <is>
+          <t>Sch. 5</t>
+        </is>
+      </c>
+      <c r="G106" s="8" t="inlineStr">
+        <is>
+          <t>ADS1115 A3, monitored (4.7k EOL resistor at the switch)</t>
+        </is>
+      </c>
+      <c r="H106" s="9" t="n"/>
+      <c r="I106" s="10">
+        <f>B106*H106</f>
+        <v/>
+      </c>
+      <c r="J106" s="11" t="n"/>
+      <c r="K106" s="12" t="n"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="6" t="n">
+        <v>79</v>
+      </c>
+      <c r="B107" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C107" s="8" t="inlineStr">
+        <is>
+          <t>Fuel sender</t>
+        </is>
+      </c>
+      <c r="D107" s="8" t="inlineStr">
+        <is>
+          <t>Original, in tank</t>
+        </is>
+      </c>
+      <c r="E107" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F107" s="6" t="inlineStr">
+        <is>
+          <t>Sch. 4</t>
+        </is>
+      </c>
+      <c r="G107" s="8" t="inlineStr">
+        <is>
+          <t>Calibrate with dash.py --calibrate</t>
+        </is>
+      </c>
+      <c r="H107" s="9" t="n"/>
+      <c r="I107" s="10">
+        <f>B107*H107</f>
+        <v/>
+      </c>
+      <c r="J107" s="11" t="n"/>
+      <c r="K107" s="12" t="n"/>
+    </row>
+    <row r="108">
+      <c r="G108" s="13" t="inlineStr">
         <is>
           <t>Subtotal — Existing Machine Parts</t>
         </is>
       </c>
-      <c r="I100" s="14">
-        <f>SUM(I96:I99)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="102">
-      <c r="G102" s="15" t="inlineStr">
+      <c r="I108" s="14">
+        <f>SUM(I104:I107)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="110">
+      <c r="G110" s="15" t="inlineStr">
         <is>
           <t>TOTAL (all sections)</t>
         </is>
       </c>
-      <c r="I102" s="16">
-        <f>I13+I19+I33+I39+I50+I58+I67+I73+I78+I83+I94+I100</f>
-        <v/>
-      </c>
-    </row>
-    <row r="103">
-      <c r="G103" s="17" t="inlineStr">
+      <c r="I110" s="16">
+        <f>I13+I19+I33+I39+I50+I58+I67+I73+I86+I91+I102+I108</f>
+        <v/>
+      </c>
+    </row>
+    <row r="111">
+      <c r="G111" s="17" t="inlineStr">
         <is>
           <t>Items still to order (excl. existing parts)</t>
         </is>
       </c>
-      <c r="I103" s="18">
-        <f>COUNTIF(B6:B94,"&gt;0")-COUNTIF(K6:K94,"Y")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="19" t="inlineStr">
+      <c r="I111" s="18">
+        <f>COUNTIF(B6:B102,"&gt;0")-COUNTIF(K6:K102,"Y")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="19" t="inlineStr">
         <is>
           <t>Notes: Qty in blue = quantity per machine. Existing machine parts usually cost $0 unless one needs replacing. Prices are left blank on purpose. Enter what you actually pay.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A5:K100"/>
+  <autoFilter ref="A5:K108"/>
   <mergeCells count="1">
     <mergeCell ref="A3:K3"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="K7 K8 K9 K10 K11 K12 K15 K16 K17 K18 K21 K22 K23 K24 K25 K26 K27 K28 K29 K30 K31 K32 K35 K36 K37 K38 K41 K42 K43 K44 K45 K46 K47 K48 K49 K52 K53 K54 K55 K56 K57 K60 K61 K62 K63 K64 K65 K66 K69 K70 K71 K72 K75 K76 K77 K80 K81 K82 K85 K86 K87 K88 K89 K90 K91 K92 K93 K96 K97 K98 K99" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K7 K8 K9 K10 K11 K12 K15 K16 K17 K18 K21 K22 K23 K24 K25 K26 K27 K28 K29 K30 K31 K32 K35 K36 K37 K38 K41 K42 K43 K44 K45 K46 K47 K48 K49 K52 K53 K54 K55 K56 K57 K60 K61 K62 K63 K64 K65 K66 K69 K70 K71 K72 K75 K76 K77 K78 K79 K80 K81 K82 K83 K84 K85 K88 K89 K90 K93 K94 K95 K96 K97 K98 K99 K100 K101 K104 K105 K106 K107" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Y,N"</formula1>
     </dataValidation>
   </dataValidations>
